--- a/data/outputs/ev_flex_daily_trading_report_sample.xlsx
+++ b/data/outputs/ev_flex_daily_trading_report_sample.xlsx
@@ -49,7 +49,7 @@
     <t>Generated at UTC</t>
   </si>
   <si>
-    <t>2026-08-31T14:33:08.054698+00:00</t>
+    <t>2026-09-07T13:06:49.621107+00:00</t>
   </si>
   <si>
     <t>Data status</t>
@@ -598,151 +598,151 @@
     <t>suggested_action</t>
   </si>
   <si>
-    <t>2026-08-31 14:33:06.251101+00:00</t>
-  </si>
-  <si>
-    <t>2026-08-31 14:33:06.281591+00:00</t>
-  </si>
-  <si>
-    <t>2026-08-31 14:33:06.305101+00:00</t>
-  </si>
-  <si>
-    <t>2026-08-31 14:33:06.338617+00:00</t>
-  </si>
-  <si>
-    <t>2026-08-31 14:33:06.369373+00:00</t>
-  </si>
-  <si>
-    <t>2026-08-31 14:33:06.394536+00:00</t>
-  </si>
-  <si>
-    <t>2026-08-31 14:33:06.413569+00:00</t>
-  </si>
-  <si>
-    <t>2026-08-31 14:33:06.440459+00:00</t>
-  </si>
-  <si>
-    <t>2026-08-31 14:33:06.459630+00:00</t>
-  </si>
-  <si>
-    <t>2026-08-31 14:33:06.481219+00:00</t>
-  </si>
-  <si>
-    <t>2026-08-31 14:33:06.505419+00:00</t>
-  </si>
-  <si>
-    <t>2026-08-31 14:33:06.531867+00:00</t>
-  </si>
-  <si>
-    <t>2026-08-31 14:33:06.552440+00:00</t>
-  </si>
-  <si>
-    <t>2026-08-31 14:33:06.577921+00:00</t>
-  </si>
-  <si>
-    <t>2026-08-31 14:33:06.596703+00:00</t>
-  </si>
-  <si>
-    <t>2026-08-31 14:33:06.615743+00:00</t>
-  </si>
-  <si>
-    <t>2026-08-31 14:33:06.632319+00:00</t>
-  </si>
-  <si>
-    <t>2026-08-31 14:33:06.651255+00:00</t>
-  </si>
-  <si>
-    <t>2026-08-31 14:33:06.676173+00:00</t>
-  </si>
-  <si>
-    <t>2026-08-31 14:33:06.701457+00:00</t>
-  </si>
-  <si>
-    <t>2026-08-31 14:33:06.719376+00:00</t>
-  </si>
-  <si>
-    <t>2026-08-31 14:33:06.732804+00:00</t>
-  </si>
-  <si>
-    <t>2026-08-31 14:33:06.746638+00:00</t>
-  </si>
-  <si>
-    <t>2026-08-31 14:33:06.765007+00:00</t>
-  </si>
-  <si>
-    <t>2026-08-31 14:33:06.817752+00:00</t>
-  </si>
-  <si>
-    <t>2026-08-31 14:33:06.878504+00:00</t>
-  </si>
-  <si>
-    <t>2026-08-31 14:33:06.901414+00:00</t>
-  </si>
-  <si>
-    <t>2026-08-31 14:33:06.934066+00:00</t>
-  </si>
-  <si>
-    <t>2026-08-31 14:33:06.961739+00:00</t>
-  </si>
-  <si>
-    <t>2026-08-31 14:33:06.986898+00:00</t>
-  </si>
-  <si>
-    <t>2026-08-31 14:33:07.005564+00:00</t>
-  </si>
-  <si>
-    <t>2026-08-31 14:33:07.032351+00:00</t>
-  </si>
-  <si>
-    <t>2026-08-31 14:33:07.051491+00:00</t>
-  </si>
-  <si>
-    <t>2026-08-31 14:33:07.073137+00:00</t>
-  </si>
-  <si>
-    <t>2026-08-31 14:33:07.097518+00:00</t>
-  </si>
-  <si>
-    <t>2026-08-31 14:33:07.123932+00:00</t>
-  </si>
-  <si>
-    <t>2026-08-31 14:33:07.144175+00:00</t>
-  </si>
-  <si>
-    <t>2026-08-31 14:33:07.169969+00:00</t>
-  </si>
-  <si>
-    <t>2026-08-31 14:33:07.188778+00:00</t>
-  </si>
-  <si>
-    <t>2026-08-31 14:33:07.207735+00:00</t>
-  </si>
-  <si>
-    <t>2026-08-31 14:33:07.224391+00:00</t>
-  </si>
-  <si>
-    <t>2026-08-31 14:33:07.243226+00:00</t>
-  </si>
-  <si>
-    <t>2026-08-31 14:33:07.268385+00:00</t>
-  </si>
-  <si>
-    <t>2026-08-31 14:33:07.293986+00:00</t>
-  </si>
-  <si>
-    <t>2026-08-31 14:33:07.311675+00:00</t>
-  </si>
-  <si>
-    <t>2026-08-31 14:33:07.325288+00:00</t>
-  </si>
-  <si>
-    <t>2026-08-31 14:33:07.338957+00:00</t>
-  </si>
-  <si>
-    <t>2026-08-31 14:33:07.357447+00:00</t>
-  </si>
-  <si>
-    <t>2026-08-31 14:33:07.489763+00:00</t>
+    <t>2026-09-07 13:06:47.791752+00:00</t>
+  </si>
+  <si>
+    <t>2026-09-07 13:06:47.824756+00:00</t>
+  </si>
+  <si>
+    <t>2026-09-07 13:06:47.851543+00:00</t>
+  </si>
+  <si>
+    <t>2026-09-07 13:06:47.889280+00:00</t>
+  </si>
+  <si>
+    <t>2026-09-07 13:06:47.921706+00:00</t>
+  </si>
+  <si>
+    <t>2026-09-07 13:06:47.948874+00:00</t>
+  </si>
+  <si>
+    <t>2026-09-07 13:06:47.968851+00:00</t>
+  </si>
+  <si>
+    <t>2026-09-07 13:06:47.997824+00:00</t>
+  </si>
+  <si>
+    <t>2026-09-07 13:06:48.018384+00:00</t>
+  </si>
+  <si>
+    <t>2026-09-07 13:06:48.041921+00:00</t>
+  </si>
+  <si>
+    <t>2026-09-07 13:06:48.068182+00:00</t>
+  </si>
+  <si>
+    <t>2026-09-07 13:06:48.096465+00:00</t>
+  </si>
+  <si>
+    <t>2026-09-07 13:06:48.118449+00:00</t>
+  </si>
+  <si>
+    <t>2026-09-07 13:06:48.146125+00:00</t>
+  </si>
+  <si>
+    <t>2026-09-07 13:06:48.166353+00:00</t>
+  </si>
+  <si>
+    <t>2026-09-07 13:06:48.187008+00:00</t>
+  </si>
+  <si>
+    <t>2026-09-07 13:06:48.204865+00:00</t>
+  </si>
+  <si>
+    <t>2026-09-07 13:06:48.225228+00:00</t>
+  </si>
+  <si>
+    <t>2026-09-07 13:06:48.252123+00:00</t>
+  </si>
+  <si>
+    <t>2026-09-07 13:06:48.279854+00:00</t>
+  </si>
+  <si>
+    <t>2026-09-07 13:06:48.299452+00:00</t>
+  </si>
+  <si>
+    <t>2026-09-07 13:06:48.314164+00:00</t>
+  </si>
+  <si>
+    <t>2026-09-07 13:06:48.329089+00:00</t>
+  </si>
+  <si>
+    <t>2026-09-07 13:06:48.349210+00:00</t>
+  </si>
+  <si>
+    <t>2026-09-07 13:06:48.405933+00:00</t>
+  </si>
+  <si>
+    <t>2026-09-07 13:06:48.458216+00:00</t>
+  </si>
+  <si>
+    <t>2026-09-07 13:06:48.482859+00:00</t>
+  </si>
+  <si>
+    <t>2026-09-07 13:06:48.518256+00:00</t>
+  </si>
+  <si>
+    <t>2026-09-07 13:06:48.548360+00:00</t>
+  </si>
+  <si>
+    <t>2026-09-07 13:06:48.575662+00:00</t>
+  </si>
+  <si>
+    <t>2026-09-07 13:06:48.595788+00:00</t>
+  </si>
+  <si>
+    <t>2026-09-07 13:06:48.624649+00:00</t>
+  </si>
+  <si>
+    <t>2026-09-07 13:06:48.645138+00:00</t>
+  </si>
+  <si>
+    <t>2026-09-07 13:06:48.668478+00:00</t>
+  </si>
+  <si>
+    <t>2026-09-07 13:06:48.694886+00:00</t>
+  </si>
+  <si>
+    <t>2026-09-07 13:06:48.723584+00:00</t>
+  </si>
+  <si>
+    <t>2026-09-07 13:06:48.745600+00:00</t>
+  </si>
+  <si>
+    <t>2026-09-07 13:06:48.773461+00:00</t>
+  </si>
+  <si>
+    <t>2026-09-07 13:06:48.793658+00:00</t>
+  </si>
+  <si>
+    <t>2026-09-07 13:06:48.814212+00:00</t>
+  </si>
+  <si>
+    <t>2026-09-07 13:06:48.832022+00:00</t>
+  </si>
+  <si>
+    <t>2026-09-07 13:06:48.852519+00:00</t>
+  </si>
+  <si>
+    <t>2026-09-07 13:06:48.879830+00:00</t>
+  </si>
+  <si>
+    <t>2026-09-07 13:06:48.907183+00:00</t>
+  </si>
+  <si>
+    <t>2026-09-07 13:06:48.926496+00:00</t>
+  </si>
+  <si>
+    <t>2026-09-07 13:06:48.941380+00:00</t>
+  </si>
+  <si>
+    <t>2026-09-07 13:06:48.956293+00:00</t>
+  </si>
+  <si>
+    <t>2026-09-07 13:06:48.976314+00:00</t>
+  </si>
+  <si>
+    <t>2026-09-07 13:06:49.116804+00:00</t>
   </si>
   <si>
     <t>low</t>
@@ -1330,7 +1330,7 @@
     <t>MWh</t>
   </si>
   <si>
-    <t>2026-08-31T14:33:01.574773+00:00</t>
+    <t>2026-09-07T13:06:43.002543+00:00</t>
   </si>
   <si>
     <t>synthetic scenario: base</t>

--- a/data/outputs/ev_flex_daily_trading_report_sample.xlsx
+++ b/data/outputs/ev_flex_daily_trading_report_sample.xlsx
@@ -49,7 +49,7 @@
     <t>Generated at UTC</t>
   </si>
   <si>
-    <t>2026-09-07T13:06:49.621107+00:00</t>
+    <t>2026-09-14T13:27:52.846351+00:00</t>
   </si>
   <si>
     <t>Data status</t>
@@ -598,151 +598,151 @@
     <t>suggested_action</t>
   </si>
   <si>
-    <t>2026-09-07 13:06:47.791752+00:00</t>
-  </si>
-  <si>
-    <t>2026-09-07 13:06:47.824756+00:00</t>
-  </si>
-  <si>
-    <t>2026-09-07 13:06:47.851543+00:00</t>
-  </si>
-  <si>
-    <t>2026-09-07 13:06:47.889280+00:00</t>
-  </si>
-  <si>
-    <t>2026-09-07 13:06:47.921706+00:00</t>
-  </si>
-  <si>
-    <t>2026-09-07 13:06:47.948874+00:00</t>
-  </si>
-  <si>
-    <t>2026-09-07 13:06:47.968851+00:00</t>
-  </si>
-  <si>
-    <t>2026-09-07 13:06:47.997824+00:00</t>
-  </si>
-  <si>
-    <t>2026-09-07 13:06:48.018384+00:00</t>
-  </si>
-  <si>
-    <t>2026-09-07 13:06:48.041921+00:00</t>
-  </si>
-  <si>
-    <t>2026-09-07 13:06:48.068182+00:00</t>
-  </si>
-  <si>
-    <t>2026-09-07 13:06:48.096465+00:00</t>
-  </si>
-  <si>
-    <t>2026-09-07 13:06:48.118449+00:00</t>
-  </si>
-  <si>
-    <t>2026-09-07 13:06:48.146125+00:00</t>
-  </si>
-  <si>
-    <t>2026-09-07 13:06:48.166353+00:00</t>
-  </si>
-  <si>
-    <t>2026-09-07 13:06:48.187008+00:00</t>
-  </si>
-  <si>
-    <t>2026-09-07 13:06:48.204865+00:00</t>
-  </si>
-  <si>
-    <t>2026-09-07 13:06:48.225228+00:00</t>
-  </si>
-  <si>
-    <t>2026-09-07 13:06:48.252123+00:00</t>
-  </si>
-  <si>
-    <t>2026-09-07 13:06:48.279854+00:00</t>
-  </si>
-  <si>
-    <t>2026-09-07 13:06:48.299452+00:00</t>
-  </si>
-  <si>
-    <t>2026-09-07 13:06:48.314164+00:00</t>
-  </si>
-  <si>
-    <t>2026-09-07 13:06:48.329089+00:00</t>
-  </si>
-  <si>
-    <t>2026-09-07 13:06:48.349210+00:00</t>
-  </si>
-  <si>
-    <t>2026-09-07 13:06:48.405933+00:00</t>
-  </si>
-  <si>
-    <t>2026-09-07 13:06:48.458216+00:00</t>
-  </si>
-  <si>
-    <t>2026-09-07 13:06:48.482859+00:00</t>
-  </si>
-  <si>
-    <t>2026-09-07 13:06:48.518256+00:00</t>
-  </si>
-  <si>
-    <t>2026-09-07 13:06:48.548360+00:00</t>
-  </si>
-  <si>
-    <t>2026-09-07 13:06:48.575662+00:00</t>
-  </si>
-  <si>
-    <t>2026-09-07 13:06:48.595788+00:00</t>
-  </si>
-  <si>
-    <t>2026-09-07 13:06:48.624649+00:00</t>
-  </si>
-  <si>
-    <t>2026-09-07 13:06:48.645138+00:00</t>
-  </si>
-  <si>
-    <t>2026-09-07 13:06:48.668478+00:00</t>
-  </si>
-  <si>
-    <t>2026-09-07 13:06:48.694886+00:00</t>
-  </si>
-  <si>
-    <t>2026-09-07 13:06:48.723584+00:00</t>
-  </si>
-  <si>
-    <t>2026-09-07 13:06:48.745600+00:00</t>
-  </si>
-  <si>
-    <t>2026-09-07 13:06:48.773461+00:00</t>
-  </si>
-  <si>
-    <t>2026-09-07 13:06:48.793658+00:00</t>
-  </si>
-  <si>
-    <t>2026-09-07 13:06:48.814212+00:00</t>
-  </si>
-  <si>
-    <t>2026-09-07 13:06:48.832022+00:00</t>
-  </si>
-  <si>
-    <t>2026-09-07 13:06:48.852519+00:00</t>
-  </si>
-  <si>
-    <t>2026-09-07 13:06:48.879830+00:00</t>
-  </si>
-  <si>
-    <t>2026-09-07 13:06:48.907183+00:00</t>
-  </si>
-  <si>
-    <t>2026-09-07 13:06:48.926496+00:00</t>
-  </si>
-  <si>
-    <t>2026-09-07 13:06:48.941380+00:00</t>
-  </si>
-  <si>
-    <t>2026-09-07 13:06:48.956293+00:00</t>
-  </si>
-  <si>
-    <t>2026-09-07 13:06:48.976314+00:00</t>
-  </si>
-  <si>
-    <t>2026-09-07 13:06:49.116804+00:00</t>
+    <t>2026-09-14 13:27:51.030321+00:00</t>
+  </si>
+  <si>
+    <t>2026-09-14 13:27:51.062820+00:00</t>
+  </si>
+  <si>
+    <t>2026-09-14 13:27:51.088434+00:00</t>
+  </si>
+  <si>
+    <t>2026-09-14 13:27:51.124760+00:00</t>
+  </si>
+  <si>
+    <t>2026-09-14 13:27:51.157128+00:00</t>
+  </si>
+  <si>
+    <t>2026-09-14 13:27:51.185135+00:00</t>
+  </si>
+  <si>
+    <t>2026-09-14 13:27:51.205210+00:00</t>
+  </si>
+  <si>
+    <t>2026-09-14 13:27:51.234260+00:00</t>
+  </si>
+  <si>
+    <t>2026-09-14 13:27:51.254849+00:00</t>
+  </si>
+  <si>
+    <t>2026-09-14 13:27:51.277850+00:00</t>
+  </si>
+  <si>
+    <t>2026-09-14 13:27:51.303882+00:00</t>
+  </si>
+  <si>
+    <t>2026-09-14 13:27:51.332429+00:00</t>
+  </si>
+  <si>
+    <t>2026-09-14 13:27:51.354638+00:00</t>
+  </si>
+  <si>
+    <t>2026-09-14 13:27:51.384271+00:00</t>
+  </si>
+  <si>
+    <t>2026-09-14 13:27:51.404559+00:00</t>
+  </si>
+  <si>
+    <t>2026-09-14 13:27:51.425127+00:00</t>
+  </si>
+  <si>
+    <t>2026-09-14 13:27:51.443054+00:00</t>
+  </si>
+  <si>
+    <t>2026-09-14 13:27:51.463430+00:00</t>
+  </si>
+  <si>
+    <t>2026-09-14 13:27:51.490298+00:00</t>
+  </si>
+  <si>
+    <t>2026-09-14 13:27:51.517466+00:00</t>
+  </si>
+  <si>
+    <t>2026-09-14 13:27:51.536746+00:00</t>
+  </si>
+  <si>
+    <t>2026-09-14 13:27:51.551578+00:00</t>
+  </si>
+  <si>
+    <t>2026-09-14 13:27:51.566544+00:00</t>
+  </si>
+  <si>
+    <t>2026-09-14 13:27:51.586561+00:00</t>
+  </si>
+  <si>
+    <t>2026-09-14 13:27:51.643108+00:00</t>
+  </si>
+  <si>
+    <t>2026-09-14 13:27:51.689922+00:00</t>
+  </si>
+  <si>
+    <t>2026-09-14 13:27:51.714512+00:00</t>
+  </si>
+  <si>
+    <t>2026-09-14 13:27:51.749837+00:00</t>
+  </si>
+  <si>
+    <t>2026-09-14 13:27:51.779572+00:00</t>
+  </si>
+  <si>
+    <t>2026-09-14 13:27:51.806757+00:00</t>
+  </si>
+  <si>
+    <t>2026-09-14 13:27:51.826769+00:00</t>
+  </si>
+  <si>
+    <t>2026-09-14 13:27:51.855571+00:00</t>
+  </si>
+  <si>
+    <t>2026-09-14 13:27:51.876092+00:00</t>
+  </si>
+  <si>
+    <t>2026-09-14 13:27:51.903888+00:00</t>
+  </si>
+  <si>
+    <t>2026-09-14 13:27:51.930033+00:00</t>
+  </si>
+  <si>
+    <t>2026-09-14 13:27:51.958306+00:00</t>
+  </si>
+  <si>
+    <t>2026-09-14 13:27:51.980284+00:00</t>
+  </si>
+  <si>
+    <t>2026-09-14 13:27:52.007796+00:00</t>
+  </si>
+  <si>
+    <t>2026-09-14 13:27:52.028295+00:00</t>
+  </si>
+  <si>
+    <t>2026-09-14 13:27:52.048908+00:00</t>
+  </si>
+  <si>
+    <t>2026-09-14 13:27:52.066813+00:00</t>
+  </si>
+  <si>
+    <t>2026-09-14 13:27:52.087241+00:00</t>
+  </si>
+  <si>
+    <t>2026-09-14 13:27:52.114424+00:00</t>
+  </si>
+  <si>
+    <t>2026-09-14 13:27:52.141792+00:00</t>
+  </si>
+  <si>
+    <t>2026-09-14 13:27:52.160894+00:00</t>
+  </si>
+  <si>
+    <t>2026-09-14 13:27:52.175700+00:00</t>
+  </si>
+  <si>
+    <t>2026-09-14 13:27:52.190614+00:00</t>
+  </si>
+  <si>
+    <t>2026-09-14 13:27:52.210758+00:00</t>
+  </si>
+  <si>
+    <t>2026-09-14 13:27:52.351280+00:00</t>
   </si>
   <si>
     <t>low</t>
@@ -1330,7 +1330,7 @@
     <t>MWh</t>
   </si>
   <si>
-    <t>2026-09-07T13:06:43.002543+00:00</t>
+    <t>2026-09-14T13:27:46.192407+00:00</t>
   </si>
   <si>
     <t>synthetic scenario: base</t>

--- a/data/outputs/ev_flex_daily_trading_report_sample.xlsx
+++ b/data/outputs/ev_flex_daily_trading_report_sample.xlsx
@@ -49,7 +49,7 @@
     <t>Generated at UTC</t>
   </si>
   <si>
-    <t>2026-09-14T13:27:52.846351+00:00</t>
+    <t>2026-09-21T13:27:18.812586+00:00</t>
   </si>
   <si>
     <t>Data status</t>
@@ -598,151 +598,151 @@
     <t>suggested_action</t>
   </si>
   <si>
-    <t>2026-09-14 13:27:51.030321+00:00</t>
-  </si>
-  <si>
-    <t>2026-09-14 13:27:51.062820+00:00</t>
-  </si>
-  <si>
-    <t>2026-09-14 13:27:51.088434+00:00</t>
-  </si>
-  <si>
-    <t>2026-09-14 13:27:51.124760+00:00</t>
-  </si>
-  <si>
-    <t>2026-09-14 13:27:51.157128+00:00</t>
-  </si>
-  <si>
-    <t>2026-09-14 13:27:51.185135+00:00</t>
-  </si>
-  <si>
-    <t>2026-09-14 13:27:51.205210+00:00</t>
-  </si>
-  <si>
-    <t>2026-09-14 13:27:51.234260+00:00</t>
-  </si>
-  <si>
-    <t>2026-09-14 13:27:51.254849+00:00</t>
-  </si>
-  <si>
-    <t>2026-09-14 13:27:51.277850+00:00</t>
-  </si>
-  <si>
-    <t>2026-09-14 13:27:51.303882+00:00</t>
-  </si>
-  <si>
-    <t>2026-09-14 13:27:51.332429+00:00</t>
-  </si>
-  <si>
-    <t>2026-09-14 13:27:51.354638+00:00</t>
-  </si>
-  <si>
-    <t>2026-09-14 13:27:51.384271+00:00</t>
-  </si>
-  <si>
-    <t>2026-09-14 13:27:51.404559+00:00</t>
-  </si>
-  <si>
-    <t>2026-09-14 13:27:51.425127+00:00</t>
-  </si>
-  <si>
-    <t>2026-09-14 13:27:51.443054+00:00</t>
-  </si>
-  <si>
-    <t>2026-09-14 13:27:51.463430+00:00</t>
-  </si>
-  <si>
-    <t>2026-09-14 13:27:51.490298+00:00</t>
-  </si>
-  <si>
-    <t>2026-09-14 13:27:51.517466+00:00</t>
-  </si>
-  <si>
-    <t>2026-09-14 13:27:51.536746+00:00</t>
-  </si>
-  <si>
-    <t>2026-09-14 13:27:51.551578+00:00</t>
-  </si>
-  <si>
-    <t>2026-09-14 13:27:51.566544+00:00</t>
-  </si>
-  <si>
-    <t>2026-09-14 13:27:51.586561+00:00</t>
-  </si>
-  <si>
-    <t>2026-09-14 13:27:51.643108+00:00</t>
-  </si>
-  <si>
-    <t>2026-09-14 13:27:51.689922+00:00</t>
-  </si>
-  <si>
-    <t>2026-09-14 13:27:51.714512+00:00</t>
-  </si>
-  <si>
-    <t>2026-09-14 13:27:51.749837+00:00</t>
-  </si>
-  <si>
-    <t>2026-09-14 13:27:51.779572+00:00</t>
-  </si>
-  <si>
-    <t>2026-09-14 13:27:51.806757+00:00</t>
-  </si>
-  <si>
-    <t>2026-09-14 13:27:51.826769+00:00</t>
-  </si>
-  <si>
-    <t>2026-09-14 13:27:51.855571+00:00</t>
-  </si>
-  <si>
-    <t>2026-09-14 13:27:51.876092+00:00</t>
-  </si>
-  <si>
-    <t>2026-09-14 13:27:51.903888+00:00</t>
-  </si>
-  <si>
-    <t>2026-09-14 13:27:51.930033+00:00</t>
-  </si>
-  <si>
-    <t>2026-09-14 13:27:51.958306+00:00</t>
-  </si>
-  <si>
-    <t>2026-09-14 13:27:51.980284+00:00</t>
-  </si>
-  <si>
-    <t>2026-09-14 13:27:52.007796+00:00</t>
-  </si>
-  <si>
-    <t>2026-09-14 13:27:52.028295+00:00</t>
-  </si>
-  <si>
-    <t>2026-09-14 13:27:52.048908+00:00</t>
-  </si>
-  <si>
-    <t>2026-09-14 13:27:52.066813+00:00</t>
-  </si>
-  <si>
-    <t>2026-09-14 13:27:52.087241+00:00</t>
-  </si>
-  <si>
-    <t>2026-09-14 13:27:52.114424+00:00</t>
-  </si>
-  <si>
-    <t>2026-09-14 13:27:52.141792+00:00</t>
-  </si>
-  <si>
-    <t>2026-09-14 13:27:52.160894+00:00</t>
-  </si>
-  <si>
-    <t>2026-09-14 13:27:52.175700+00:00</t>
-  </si>
-  <si>
-    <t>2026-09-14 13:27:52.190614+00:00</t>
-  </si>
-  <si>
-    <t>2026-09-14 13:27:52.210758+00:00</t>
-  </si>
-  <si>
-    <t>2026-09-14 13:27:52.351280+00:00</t>
+    <t>2026-09-21 13:27:16.937732+00:00</t>
+  </si>
+  <si>
+    <t>2026-09-21 13:27:16.972915+00:00</t>
+  </si>
+  <si>
+    <t>2026-09-21 13:27:16.999479+00:00</t>
+  </si>
+  <si>
+    <t>2026-09-21 13:27:17.036744+00:00</t>
+  </si>
+  <si>
+    <t>2026-09-21 13:27:17.070078+00:00</t>
+  </si>
+  <si>
+    <t>2026-09-21 13:27:17.097744+00:00</t>
+  </si>
+  <si>
+    <t>2026-09-21 13:27:17.118058+00:00</t>
+  </si>
+  <si>
+    <t>2026-09-21 13:27:17.147187+00:00</t>
+  </si>
+  <si>
+    <t>2026-09-21 13:27:17.168163+00:00</t>
+  </si>
+  <si>
+    <t>2026-09-21 13:27:17.191411+00:00</t>
+  </si>
+  <si>
+    <t>2026-09-21 13:27:17.217928+00:00</t>
+  </si>
+  <si>
+    <t>2026-09-21 13:27:17.246445+00:00</t>
+  </si>
+  <si>
+    <t>2026-09-21 13:27:17.268318+00:00</t>
+  </si>
+  <si>
+    <t>2026-09-21 13:27:17.296069+00:00</t>
+  </si>
+  <si>
+    <t>2026-09-21 13:27:17.316446+00:00</t>
+  </si>
+  <si>
+    <t>2026-09-21 13:27:17.336889+00:00</t>
+  </si>
+  <si>
+    <t>2026-09-21 13:27:17.354791+00:00</t>
+  </si>
+  <si>
+    <t>2026-09-21 13:27:17.375403+00:00</t>
+  </si>
+  <si>
+    <t>2026-09-21 13:27:17.402658+00:00</t>
+  </si>
+  <si>
+    <t>2026-09-21 13:27:17.429846+00:00</t>
+  </si>
+  <si>
+    <t>2026-09-21 13:27:17.448978+00:00</t>
+  </si>
+  <si>
+    <t>2026-09-21 13:27:17.463720+00:00</t>
+  </si>
+  <si>
+    <t>2026-09-21 13:27:17.478519+00:00</t>
+  </si>
+  <si>
+    <t>2026-09-21 13:27:17.498473+00:00</t>
+  </si>
+  <si>
+    <t>2026-09-21 13:27:17.556111+00:00</t>
+  </si>
+  <si>
+    <t>2026-09-21 13:27:17.606972+00:00</t>
+  </si>
+  <si>
+    <t>2026-09-21 13:27:17.631266+00:00</t>
+  </si>
+  <si>
+    <t>2026-09-21 13:27:17.666258+00:00</t>
+  </si>
+  <si>
+    <t>2026-09-21 13:27:17.695961+00:00</t>
+  </si>
+  <si>
+    <t>2026-09-21 13:27:17.723128+00:00</t>
+  </si>
+  <si>
+    <t>2026-09-21 13:27:17.743444+00:00</t>
+  </si>
+  <si>
+    <t>2026-09-21 13:27:17.772190+00:00</t>
+  </si>
+  <si>
+    <t>2026-09-21 13:27:17.793195+00:00</t>
+  </si>
+  <si>
+    <t>2026-09-21 13:27:17.817005+00:00</t>
+  </si>
+  <si>
+    <t>2026-09-21 13:27:17.843551+00:00</t>
+  </si>
+  <si>
+    <t>2026-09-21 13:27:17.872204+00:00</t>
+  </si>
+  <si>
+    <t>2026-09-21 13:27:17.894255+00:00</t>
+  </si>
+  <si>
+    <t>2026-09-21 13:27:17.921828+00:00</t>
+  </si>
+  <si>
+    <t>2026-09-21 13:27:17.942200+00:00</t>
+  </si>
+  <si>
+    <t>2026-09-21 13:27:17.962797+00:00</t>
+  </si>
+  <si>
+    <t>2026-09-21 13:27:17.980758+00:00</t>
+  </si>
+  <si>
+    <t>2026-09-21 13:27:18.001423+00:00</t>
+  </si>
+  <si>
+    <t>2026-09-21 13:27:18.028741+00:00</t>
+  </si>
+  <si>
+    <t>2026-09-21 13:27:18.056976+00:00</t>
+  </si>
+  <si>
+    <t>2026-09-21 13:27:18.076499+00:00</t>
+  </si>
+  <si>
+    <t>2026-09-21 13:27:18.091443+00:00</t>
+  </si>
+  <si>
+    <t>2026-09-21 13:27:18.106459+00:00</t>
+  </si>
+  <si>
+    <t>2026-09-21 13:27:18.126762+00:00</t>
+  </si>
+  <si>
+    <t>2026-09-21 13:27:18.272154+00:00</t>
   </si>
   <si>
     <t>low</t>
@@ -1330,7 +1330,7 @@
     <t>MWh</t>
   </si>
   <si>
-    <t>2026-09-14T13:27:46.192407+00:00</t>
+    <t>2026-09-21T13:27:11.913599+00:00</t>
   </si>
   <si>
     <t>synthetic scenario: base</t>

--- a/data/outputs/ev_flex_daily_trading_report_sample.xlsx
+++ b/data/outputs/ev_flex_daily_trading_report_sample.xlsx
@@ -49,7 +49,7 @@
     <t>Generated at UTC</t>
   </si>
   <si>
-    <t>2026-09-21T13:27:18.812586+00:00</t>
+    <t>2026-09-28T14:41:05.207043+00:00</t>
   </si>
   <si>
     <t>Data status</t>
@@ -598,151 +598,151 @@
     <t>suggested_action</t>
   </si>
   <si>
-    <t>2026-09-21 13:27:16.937732+00:00</t>
-  </si>
-  <si>
-    <t>2026-09-21 13:27:16.972915+00:00</t>
-  </si>
-  <si>
-    <t>2026-09-21 13:27:16.999479+00:00</t>
-  </si>
-  <si>
-    <t>2026-09-21 13:27:17.036744+00:00</t>
-  </si>
-  <si>
-    <t>2026-09-21 13:27:17.070078+00:00</t>
-  </si>
-  <si>
-    <t>2026-09-21 13:27:17.097744+00:00</t>
-  </si>
-  <si>
-    <t>2026-09-21 13:27:17.118058+00:00</t>
-  </si>
-  <si>
-    <t>2026-09-21 13:27:17.147187+00:00</t>
-  </si>
-  <si>
-    <t>2026-09-21 13:27:17.168163+00:00</t>
-  </si>
-  <si>
-    <t>2026-09-21 13:27:17.191411+00:00</t>
-  </si>
-  <si>
-    <t>2026-09-21 13:27:17.217928+00:00</t>
-  </si>
-  <si>
-    <t>2026-09-21 13:27:17.246445+00:00</t>
-  </si>
-  <si>
-    <t>2026-09-21 13:27:17.268318+00:00</t>
-  </si>
-  <si>
-    <t>2026-09-21 13:27:17.296069+00:00</t>
-  </si>
-  <si>
-    <t>2026-09-21 13:27:17.316446+00:00</t>
-  </si>
-  <si>
-    <t>2026-09-21 13:27:17.336889+00:00</t>
-  </si>
-  <si>
-    <t>2026-09-21 13:27:17.354791+00:00</t>
-  </si>
-  <si>
-    <t>2026-09-21 13:27:17.375403+00:00</t>
-  </si>
-  <si>
-    <t>2026-09-21 13:27:17.402658+00:00</t>
-  </si>
-  <si>
-    <t>2026-09-21 13:27:17.429846+00:00</t>
-  </si>
-  <si>
-    <t>2026-09-21 13:27:17.448978+00:00</t>
-  </si>
-  <si>
-    <t>2026-09-21 13:27:17.463720+00:00</t>
-  </si>
-  <si>
-    <t>2026-09-21 13:27:17.478519+00:00</t>
-  </si>
-  <si>
-    <t>2026-09-21 13:27:17.498473+00:00</t>
-  </si>
-  <si>
-    <t>2026-09-21 13:27:17.556111+00:00</t>
-  </si>
-  <si>
-    <t>2026-09-21 13:27:17.606972+00:00</t>
-  </si>
-  <si>
-    <t>2026-09-21 13:27:17.631266+00:00</t>
-  </si>
-  <si>
-    <t>2026-09-21 13:27:17.666258+00:00</t>
-  </si>
-  <si>
-    <t>2026-09-21 13:27:17.695961+00:00</t>
-  </si>
-  <si>
-    <t>2026-09-21 13:27:17.723128+00:00</t>
-  </si>
-  <si>
-    <t>2026-09-21 13:27:17.743444+00:00</t>
-  </si>
-  <si>
-    <t>2026-09-21 13:27:17.772190+00:00</t>
-  </si>
-  <si>
-    <t>2026-09-21 13:27:17.793195+00:00</t>
-  </si>
-  <si>
-    <t>2026-09-21 13:27:17.817005+00:00</t>
-  </si>
-  <si>
-    <t>2026-09-21 13:27:17.843551+00:00</t>
-  </si>
-  <si>
-    <t>2026-09-21 13:27:17.872204+00:00</t>
-  </si>
-  <si>
-    <t>2026-09-21 13:27:17.894255+00:00</t>
-  </si>
-  <si>
-    <t>2026-09-21 13:27:17.921828+00:00</t>
-  </si>
-  <si>
-    <t>2026-09-21 13:27:17.942200+00:00</t>
-  </si>
-  <si>
-    <t>2026-09-21 13:27:17.962797+00:00</t>
-  </si>
-  <si>
-    <t>2026-09-21 13:27:17.980758+00:00</t>
-  </si>
-  <si>
-    <t>2026-09-21 13:27:18.001423+00:00</t>
-  </si>
-  <si>
-    <t>2026-09-21 13:27:18.028741+00:00</t>
-  </si>
-  <si>
-    <t>2026-09-21 13:27:18.056976+00:00</t>
-  </si>
-  <si>
-    <t>2026-09-21 13:27:18.076499+00:00</t>
-  </si>
-  <si>
-    <t>2026-09-21 13:27:18.091443+00:00</t>
-  </si>
-  <si>
-    <t>2026-09-21 13:27:18.106459+00:00</t>
-  </si>
-  <si>
-    <t>2026-09-21 13:27:18.126762+00:00</t>
-  </si>
-  <si>
-    <t>2026-09-21 13:27:18.272154+00:00</t>
+    <t>2026-09-28 14:41:03.407916+00:00</t>
+  </si>
+  <si>
+    <t>2026-09-28 14:41:03.439879+00:00</t>
+  </si>
+  <si>
+    <t>2026-09-28 14:41:03.466188+00:00</t>
+  </si>
+  <si>
+    <t>2026-09-28 14:41:03.502609+00:00</t>
+  </si>
+  <si>
+    <t>2026-09-28 14:41:03.534331+00:00</t>
+  </si>
+  <si>
+    <t>2026-09-28 14:41:03.562586+00:00</t>
+  </si>
+  <si>
+    <t>2026-09-28 14:41:03.582276+00:00</t>
+  </si>
+  <si>
+    <t>2026-09-28 14:41:03.610336+00:00</t>
+  </si>
+  <si>
+    <t>2026-09-28 14:41:03.630136+00:00</t>
+  </si>
+  <si>
+    <t>2026-09-28 14:41:03.653408+00:00</t>
+  </si>
+  <si>
+    <t>2026-09-28 14:41:03.678765+00:00</t>
+  </si>
+  <si>
+    <t>2026-09-28 14:41:03.706444+00:00</t>
+  </si>
+  <si>
+    <t>2026-09-28 14:41:03.727735+00:00</t>
+  </si>
+  <si>
+    <t>2026-09-28 14:41:03.754791+00:00</t>
+  </si>
+  <si>
+    <t>2026-09-28 14:41:03.774748+00:00</t>
+  </si>
+  <si>
+    <t>2026-09-28 14:41:03.794724+00:00</t>
+  </si>
+  <si>
+    <t>2026-09-28 14:41:03.812489+00:00</t>
+  </si>
+  <si>
+    <t>2026-09-28 14:41:03.832440+00:00</t>
+  </si>
+  <si>
+    <t>2026-09-28 14:41:03.859586+00:00</t>
+  </si>
+  <si>
+    <t>2026-09-28 14:41:03.886239+00:00</t>
+  </si>
+  <si>
+    <t>2026-09-28 14:41:03.905396+00:00</t>
+  </si>
+  <si>
+    <t>2026-09-28 14:41:03.919925+00:00</t>
+  </si>
+  <si>
+    <t>2026-09-28 14:41:03.934342+00:00</t>
+  </si>
+  <si>
+    <t>2026-09-28 14:41:03.953851+00:00</t>
+  </si>
+  <si>
+    <t>2026-09-28 14:41:04.010283+00:00</t>
+  </si>
+  <si>
+    <t>2026-09-28 14:41:04.056956+00:00</t>
+  </si>
+  <si>
+    <t>2026-09-28 14:41:04.080842+00:00</t>
+  </si>
+  <si>
+    <t>2026-09-28 14:41:04.115517+00:00</t>
+  </si>
+  <si>
+    <t>2026-09-28 14:41:04.145011+00:00</t>
+  </si>
+  <si>
+    <t>2026-09-28 14:41:04.171985+00:00</t>
+  </si>
+  <si>
+    <t>2026-09-28 14:41:04.191795+00:00</t>
+  </si>
+  <si>
+    <t>2026-09-28 14:41:04.220309+00:00</t>
+  </si>
+  <si>
+    <t>2026-09-28 14:41:04.240505+00:00</t>
+  </si>
+  <si>
+    <t>2026-09-28 14:41:04.263589+00:00</t>
+  </si>
+  <si>
+    <t>2026-09-28 14:41:04.289509+00:00</t>
+  </si>
+  <si>
+    <t>2026-09-28 14:41:04.317543+00:00</t>
+  </si>
+  <si>
+    <t>2026-09-28 14:41:04.339155+00:00</t>
+  </si>
+  <si>
+    <t>2026-09-28 14:41:04.366345+00:00</t>
+  </si>
+  <si>
+    <t>2026-09-28 14:41:04.386385+00:00</t>
+  </si>
+  <si>
+    <t>2026-09-28 14:41:04.406587+00:00</t>
+  </si>
+  <si>
+    <t>2026-09-28 14:41:04.424165+00:00</t>
+  </si>
+  <si>
+    <t>2026-09-28 14:41:04.444311+00:00</t>
+  </si>
+  <si>
+    <t>2026-09-28 14:41:04.471020+00:00</t>
+  </si>
+  <si>
+    <t>2026-09-28 14:41:04.498189+00:00</t>
+  </si>
+  <si>
+    <t>2026-09-28 14:41:04.517151+00:00</t>
+  </si>
+  <si>
+    <t>2026-09-28 14:41:04.531741+00:00</t>
+  </si>
+  <si>
+    <t>2026-09-28 14:41:04.546449+00:00</t>
+  </si>
+  <si>
+    <t>2026-09-28 14:41:04.566325+00:00</t>
+  </si>
+  <si>
+    <t>2026-09-28 14:41:04.705717+00:00</t>
   </si>
   <si>
     <t>low</t>
@@ -1330,7 +1330,7 @@
     <t>MWh</t>
   </si>
   <si>
-    <t>2026-09-21T13:27:11.913599+00:00</t>
+    <t>2026-09-28T14:40:58.565085+00:00</t>
   </si>
   <si>
     <t>synthetic scenario: base</t>

--- a/data/outputs/ev_flex_daily_trading_report_sample.xlsx
+++ b/data/outputs/ev_flex_daily_trading_report_sample.xlsx
@@ -49,7 +49,7 @@
     <t>Generated at UTC</t>
   </si>
   <si>
-    <t>2026-09-28T14:41:05.207043+00:00</t>
+    <t>2026-10-05T15:23:05.984347+00:00</t>
   </si>
   <si>
     <t>Data status</t>
@@ -598,151 +598,151 @@
     <t>suggested_action</t>
   </si>
   <si>
-    <t>2026-09-28 14:41:03.407916+00:00</t>
-  </si>
-  <si>
-    <t>2026-09-28 14:41:03.439879+00:00</t>
-  </si>
-  <si>
-    <t>2026-09-28 14:41:03.466188+00:00</t>
-  </si>
-  <si>
-    <t>2026-09-28 14:41:03.502609+00:00</t>
-  </si>
-  <si>
-    <t>2026-09-28 14:41:03.534331+00:00</t>
-  </si>
-  <si>
-    <t>2026-09-28 14:41:03.562586+00:00</t>
-  </si>
-  <si>
-    <t>2026-09-28 14:41:03.582276+00:00</t>
-  </si>
-  <si>
-    <t>2026-09-28 14:41:03.610336+00:00</t>
-  </si>
-  <si>
-    <t>2026-09-28 14:41:03.630136+00:00</t>
-  </si>
-  <si>
-    <t>2026-09-28 14:41:03.653408+00:00</t>
-  </si>
-  <si>
-    <t>2026-09-28 14:41:03.678765+00:00</t>
-  </si>
-  <si>
-    <t>2026-09-28 14:41:03.706444+00:00</t>
-  </si>
-  <si>
-    <t>2026-09-28 14:41:03.727735+00:00</t>
-  </si>
-  <si>
-    <t>2026-09-28 14:41:03.754791+00:00</t>
-  </si>
-  <si>
-    <t>2026-09-28 14:41:03.774748+00:00</t>
-  </si>
-  <si>
-    <t>2026-09-28 14:41:03.794724+00:00</t>
-  </si>
-  <si>
-    <t>2026-09-28 14:41:03.812489+00:00</t>
-  </si>
-  <si>
-    <t>2026-09-28 14:41:03.832440+00:00</t>
-  </si>
-  <si>
-    <t>2026-09-28 14:41:03.859586+00:00</t>
-  </si>
-  <si>
-    <t>2026-09-28 14:41:03.886239+00:00</t>
-  </si>
-  <si>
-    <t>2026-09-28 14:41:03.905396+00:00</t>
-  </si>
-  <si>
-    <t>2026-09-28 14:41:03.919925+00:00</t>
-  </si>
-  <si>
-    <t>2026-09-28 14:41:03.934342+00:00</t>
-  </si>
-  <si>
-    <t>2026-09-28 14:41:03.953851+00:00</t>
-  </si>
-  <si>
-    <t>2026-09-28 14:41:04.010283+00:00</t>
-  </si>
-  <si>
-    <t>2026-09-28 14:41:04.056956+00:00</t>
-  </si>
-  <si>
-    <t>2026-09-28 14:41:04.080842+00:00</t>
-  </si>
-  <si>
-    <t>2026-09-28 14:41:04.115517+00:00</t>
-  </si>
-  <si>
-    <t>2026-09-28 14:41:04.145011+00:00</t>
-  </si>
-  <si>
-    <t>2026-09-28 14:41:04.171985+00:00</t>
-  </si>
-  <si>
-    <t>2026-09-28 14:41:04.191795+00:00</t>
-  </si>
-  <si>
-    <t>2026-09-28 14:41:04.220309+00:00</t>
-  </si>
-  <si>
-    <t>2026-09-28 14:41:04.240505+00:00</t>
-  </si>
-  <si>
-    <t>2026-09-28 14:41:04.263589+00:00</t>
-  </si>
-  <si>
-    <t>2026-09-28 14:41:04.289509+00:00</t>
-  </si>
-  <si>
-    <t>2026-09-28 14:41:04.317543+00:00</t>
-  </si>
-  <si>
-    <t>2026-09-28 14:41:04.339155+00:00</t>
-  </si>
-  <si>
-    <t>2026-09-28 14:41:04.366345+00:00</t>
-  </si>
-  <si>
-    <t>2026-09-28 14:41:04.386385+00:00</t>
-  </si>
-  <si>
-    <t>2026-09-28 14:41:04.406587+00:00</t>
-  </si>
-  <si>
-    <t>2026-09-28 14:41:04.424165+00:00</t>
-  </si>
-  <si>
-    <t>2026-09-28 14:41:04.444311+00:00</t>
-  </si>
-  <si>
-    <t>2026-09-28 14:41:04.471020+00:00</t>
-  </si>
-  <si>
-    <t>2026-09-28 14:41:04.498189+00:00</t>
-  </si>
-  <si>
-    <t>2026-09-28 14:41:04.517151+00:00</t>
-  </si>
-  <si>
-    <t>2026-09-28 14:41:04.531741+00:00</t>
-  </si>
-  <si>
-    <t>2026-09-28 14:41:04.546449+00:00</t>
-  </si>
-  <si>
-    <t>2026-09-28 14:41:04.566325+00:00</t>
-  </si>
-  <si>
-    <t>2026-09-28 14:41:04.705717+00:00</t>
+    <t>2026-10-05 15:23:04.143922+00:00</t>
+  </si>
+  <si>
+    <t>2026-10-05 15:23:04.177074+00:00</t>
+  </si>
+  <si>
+    <t>2026-10-05 15:23:04.202950+00:00</t>
+  </si>
+  <si>
+    <t>2026-10-05 15:23:04.246658+00:00</t>
+  </si>
+  <si>
+    <t>2026-10-05 15:23:04.279638+00:00</t>
+  </si>
+  <si>
+    <t>2026-10-05 15:23:04.307013+00:00</t>
+  </si>
+  <si>
+    <t>2026-10-05 15:23:04.327249+00:00</t>
+  </si>
+  <si>
+    <t>2026-10-05 15:23:04.356317+00:00</t>
+  </si>
+  <si>
+    <t>2026-10-05 15:23:04.376975+00:00</t>
+  </si>
+  <si>
+    <t>2026-10-05 15:23:04.400098+00:00</t>
+  </si>
+  <si>
+    <t>2026-10-05 15:23:04.426383+00:00</t>
+  </si>
+  <si>
+    <t>2026-10-05 15:23:04.454900+00:00</t>
+  </si>
+  <si>
+    <t>2026-10-05 15:23:04.476895+00:00</t>
+  </si>
+  <si>
+    <t>2026-10-05 15:23:04.504614+00:00</t>
+  </si>
+  <si>
+    <t>2026-10-05 15:23:04.524972+00:00</t>
+  </si>
+  <si>
+    <t>2026-10-05 15:23:04.545567+00:00</t>
+  </si>
+  <si>
+    <t>2026-10-05 15:23:04.563513+00:00</t>
+  </si>
+  <si>
+    <t>2026-10-05 15:23:04.584059+00:00</t>
+  </si>
+  <si>
+    <t>2026-10-05 15:23:04.611213+00:00</t>
+  </si>
+  <si>
+    <t>2026-10-05 15:23:04.638661+00:00</t>
+  </si>
+  <si>
+    <t>2026-10-05 15:23:04.658159+00:00</t>
+  </si>
+  <si>
+    <t>2026-10-05 15:23:04.673098+00:00</t>
+  </si>
+  <si>
+    <t>2026-10-05 15:23:04.687866+00:00</t>
+  </si>
+  <si>
+    <t>2026-10-05 15:23:04.707893+00:00</t>
+  </si>
+  <si>
+    <t>2026-10-05 15:23:04.765253+00:00</t>
+  </si>
+  <si>
+    <t>2026-10-05 15:23:04.813817+00:00</t>
+  </si>
+  <si>
+    <t>2026-10-05 15:23:04.838551+00:00</t>
+  </si>
+  <si>
+    <t>2026-10-05 15:23:04.873970+00:00</t>
+  </si>
+  <si>
+    <t>2026-10-05 15:23:04.904081+00:00</t>
+  </si>
+  <si>
+    <t>2026-10-05 15:23:04.931892+00:00</t>
+  </si>
+  <si>
+    <t>2026-10-05 15:23:04.952033+00:00</t>
+  </si>
+  <si>
+    <t>2026-10-05 15:23:04.981003+00:00</t>
+  </si>
+  <si>
+    <t>2026-10-05 15:23:05.001556+00:00</t>
+  </si>
+  <si>
+    <t>2026-10-05 15:23:05.024963+00:00</t>
+  </si>
+  <si>
+    <t>2026-10-05 15:23:05.051376+00:00</t>
+  </si>
+  <si>
+    <t>2026-10-05 15:23:05.079902+00:00</t>
+  </si>
+  <si>
+    <t>2026-10-05 15:23:05.102033+00:00</t>
+  </si>
+  <si>
+    <t>2026-10-05 15:23:05.129883+00:00</t>
+  </si>
+  <si>
+    <t>2026-10-05 15:23:05.150515+00:00</t>
+  </si>
+  <si>
+    <t>2026-10-05 15:23:05.171108+00:00</t>
+  </si>
+  <si>
+    <t>2026-10-05 15:23:05.189065+00:00</t>
+  </si>
+  <si>
+    <t>2026-10-05 15:23:05.209753+00:00</t>
+  </si>
+  <si>
+    <t>2026-10-05 15:23:05.237023+00:00</t>
+  </si>
+  <si>
+    <t>2026-10-05 15:23:05.264646+00:00</t>
+  </si>
+  <si>
+    <t>2026-10-05 15:23:05.284062+00:00</t>
+  </si>
+  <si>
+    <t>2026-10-05 15:23:05.299010+00:00</t>
+  </si>
+  <si>
+    <t>2026-10-05 15:23:05.314111+00:00</t>
+  </si>
+  <si>
+    <t>2026-10-05 15:23:05.334132+00:00</t>
+  </si>
+  <si>
+    <t>2026-10-05 15:23:05.477618+00:00</t>
   </si>
   <si>
     <t>low</t>
@@ -1330,7 +1330,7 @@
     <t>MWh</t>
   </si>
   <si>
-    <t>2026-09-28T14:40:58.565085+00:00</t>
+    <t>2026-10-05T15:22:59.271131+00:00</t>
   </si>
   <si>
     <t>synthetic scenario: base</t>

--- a/data/outputs/ev_flex_daily_trading_report_sample.xlsx
+++ b/data/outputs/ev_flex_daily_trading_report_sample.xlsx
@@ -49,7 +49,7 @@
     <t>Generated at UTC</t>
   </si>
   <si>
-    <t>2026-10-05T15:23:05.984347+00:00</t>
+    <t>2026-10-12T16:15:29.887687+00:00</t>
   </si>
   <si>
     <t>Data status</t>
@@ -598,151 +598,151 @@
     <t>suggested_action</t>
   </si>
   <si>
-    <t>2026-10-05 15:23:04.143922+00:00</t>
-  </si>
-  <si>
-    <t>2026-10-05 15:23:04.177074+00:00</t>
-  </si>
-  <si>
-    <t>2026-10-05 15:23:04.202950+00:00</t>
-  </si>
-  <si>
-    <t>2026-10-05 15:23:04.246658+00:00</t>
-  </si>
-  <si>
-    <t>2026-10-05 15:23:04.279638+00:00</t>
-  </si>
-  <si>
-    <t>2026-10-05 15:23:04.307013+00:00</t>
-  </si>
-  <si>
-    <t>2026-10-05 15:23:04.327249+00:00</t>
-  </si>
-  <si>
-    <t>2026-10-05 15:23:04.356317+00:00</t>
-  </si>
-  <si>
-    <t>2026-10-05 15:23:04.376975+00:00</t>
-  </si>
-  <si>
-    <t>2026-10-05 15:23:04.400098+00:00</t>
-  </si>
-  <si>
-    <t>2026-10-05 15:23:04.426383+00:00</t>
-  </si>
-  <si>
-    <t>2026-10-05 15:23:04.454900+00:00</t>
-  </si>
-  <si>
-    <t>2026-10-05 15:23:04.476895+00:00</t>
-  </si>
-  <si>
-    <t>2026-10-05 15:23:04.504614+00:00</t>
-  </si>
-  <si>
-    <t>2026-10-05 15:23:04.524972+00:00</t>
-  </si>
-  <si>
-    <t>2026-10-05 15:23:04.545567+00:00</t>
-  </si>
-  <si>
-    <t>2026-10-05 15:23:04.563513+00:00</t>
-  </si>
-  <si>
-    <t>2026-10-05 15:23:04.584059+00:00</t>
-  </si>
-  <si>
-    <t>2026-10-05 15:23:04.611213+00:00</t>
-  </si>
-  <si>
-    <t>2026-10-05 15:23:04.638661+00:00</t>
-  </si>
-  <si>
-    <t>2026-10-05 15:23:04.658159+00:00</t>
-  </si>
-  <si>
-    <t>2026-10-05 15:23:04.673098+00:00</t>
-  </si>
-  <si>
-    <t>2026-10-05 15:23:04.687866+00:00</t>
-  </si>
-  <si>
-    <t>2026-10-05 15:23:04.707893+00:00</t>
-  </si>
-  <si>
-    <t>2026-10-05 15:23:04.765253+00:00</t>
-  </si>
-  <si>
-    <t>2026-10-05 15:23:04.813817+00:00</t>
-  </si>
-  <si>
-    <t>2026-10-05 15:23:04.838551+00:00</t>
-  </si>
-  <si>
-    <t>2026-10-05 15:23:04.873970+00:00</t>
-  </si>
-  <si>
-    <t>2026-10-05 15:23:04.904081+00:00</t>
-  </si>
-  <si>
-    <t>2026-10-05 15:23:04.931892+00:00</t>
-  </si>
-  <si>
-    <t>2026-10-05 15:23:04.952033+00:00</t>
-  </si>
-  <si>
-    <t>2026-10-05 15:23:04.981003+00:00</t>
-  </si>
-  <si>
-    <t>2026-10-05 15:23:05.001556+00:00</t>
-  </si>
-  <si>
-    <t>2026-10-05 15:23:05.024963+00:00</t>
-  </si>
-  <si>
-    <t>2026-10-05 15:23:05.051376+00:00</t>
-  </si>
-  <si>
-    <t>2026-10-05 15:23:05.079902+00:00</t>
-  </si>
-  <si>
-    <t>2026-10-05 15:23:05.102033+00:00</t>
-  </si>
-  <si>
-    <t>2026-10-05 15:23:05.129883+00:00</t>
-  </si>
-  <si>
-    <t>2026-10-05 15:23:05.150515+00:00</t>
-  </si>
-  <si>
-    <t>2026-10-05 15:23:05.171108+00:00</t>
-  </si>
-  <si>
-    <t>2026-10-05 15:23:05.189065+00:00</t>
-  </si>
-  <si>
-    <t>2026-10-05 15:23:05.209753+00:00</t>
-  </si>
-  <si>
-    <t>2026-10-05 15:23:05.237023+00:00</t>
-  </si>
-  <si>
-    <t>2026-10-05 15:23:05.264646+00:00</t>
-  </si>
-  <si>
-    <t>2026-10-05 15:23:05.284062+00:00</t>
-  </si>
-  <si>
-    <t>2026-10-05 15:23:05.299010+00:00</t>
-  </si>
-  <si>
-    <t>2026-10-05 15:23:05.314111+00:00</t>
-  </si>
-  <si>
-    <t>2026-10-05 15:23:05.334132+00:00</t>
-  </si>
-  <si>
-    <t>2026-10-05 15:23:05.477618+00:00</t>
+    <t>2026-10-12 16:15:28.217838+00:00</t>
+  </si>
+  <si>
+    <t>2026-10-12 16:15:28.247497+00:00</t>
+  </si>
+  <si>
+    <t>2026-10-12 16:15:28.271987+00:00</t>
+  </si>
+  <si>
+    <t>2026-10-12 16:15:28.304943+00:00</t>
+  </si>
+  <si>
+    <t>2026-10-12 16:15:28.333868+00:00</t>
+  </si>
+  <si>
+    <t>2026-10-12 16:15:28.358228+00:00</t>
+  </si>
+  <si>
+    <t>2026-10-12 16:15:28.375913+00:00</t>
+  </si>
+  <si>
+    <t>2026-10-12 16:15:28.401483+00:00</t>
+  </si>
+  <si>
+    <t>2026-10-12 16:15:28.419661+00:00</t>
+  </si>
+  <si>
+    <t>2026-10-12 16:15:28.439974+00:00</t>
+  </si>
+  <si>
+    <t>2026-10-12 16:15:28.463334+00:00</t>
+  </si>
+  <si>
+    <t>2026-10-12 16:15:28.488509+00:00</t>
+  </si>
+  <si>
+    <t>2026-10-12 16:15:28.507901+00:00</t>
+  </si>
+  <si>
+    <t>2026-10-12 16:15:28.532235+00:00</t>
+  </si>
+  <si>
+    <t>2026-10-12 16:15:28.550205+00:00</t>
+  </si>
+  <si>
+    <t>2026-10-12 16:15:28.568272+00:00</t>
+  </si>
+  <si>
+    <t>2026-10-12 16:15:28.584114+00:00</t>
+  </si>
+  <si>
+    <t>2026-10-12 16:15:28.602455+00:00</t>
+  </si>
+  <si>
+    <t>2026-10-12 16:15:28.626417+00:00</t>
+  </si>
+  <si>
+    <t>2026-10-12 16:15:28.650639+00:00</t>
+  </si>
+  <si>
+    <t>2026-10-12 16:15:28.667863+00:00</t>
+  </si>
+  <si>
+    <t>2026-10-12 16:15:28.681019+00:00</t>
+  </si>
+  <si>
+    <t>2026-10-12 16:15:28.694095+00:00</t>
+  </si>
+  <si>
+    <t>2026-10-12 16:15:28.712002+00:00</t>
+  </si>
+  <si>
+    <t>2026-10-12 16:15:28.762555+00:00</t>
+  </si>
+  <si>
+    <t>2026-10-12 16:15:28.811978+00:00</t>
+  </si>
+  <si>
+    <t>2026-10-12 16:15:28.833698+00:00</t>
+  </si>
+  <si>
+    <t>2026-10-12 16:15:28.864831+00:00</t>
+  </si>
+  <si>
+    <t>2026-10-12 16:15:28.891135+00:00</t>
+  </si>
+  <si>
+    <t>2026-10-12 16:15:28.915330+00:00</t>
+  </si>
+  <si>
+    <t>2026-10-12 16:15:28.933189+00:00</t>
+  </si>
+  <si>
+    <t>2026-10-12 16:15:28.958886+00:00</t>
+  </si>
+  <si>
+    <t>2026-10-12 16:15:28.977045+00:00</t>
+  </si>
+  <si>
+    <t>2026-10-12 16:15:28.997765+00:00</t>
+  </si>
+  <si>
+    <t>2026-10-12 16:15:29.021020+00:00</t>
+  </si>
+  <si>
+    <t>2026-10-12 16:15:29.046190+00:00</t>
+  </si>
+  <si>
+    <t>2026-10-12 16:15:29.065715+00:00</t>
+  </si>
+  <si>
+    <t>2026-10-12 16:15:29.090263+00:00</t>
+  </si>
+  <si>
+    <t>2026-10-12 16:15:29.108151+00:00</t>
+  </si>
+  <si>
+    <t>2026-10-12 16:15:29.126542+00:00</t>
+  </si>
+  <si>
+    <t>2026-10-12 16:15:29.142323+00:00</t>
+  </si>
+  <si>
+    <t>2026-10-12 16:15:29.160486+00:00</t>
+  </si>
+  <si>
+    <t>2026-10-12 16:15:29.184364+00:00</t>
+  </si>
+  <si>
+    <t>2026-10-12 16:15:29.208992+00:00</t>
+  </si>
+  <si>
+    <t>2026-10-12 16:15:29.226104+00:00</t>
+  </si>
+  <si>
+    <t>2026-10-12 16:15:29.239248+00:00</t>
+  </si>
+  <si>
+    <t>2026-10-12 16:15:29.252354+00:00</t>
+  </si>
+  <si>
+    <t>2026-10-12 16:15:29.270367+00:00</t>
+  </si>
+  <si>
+    <t>2026-10-12 16:15:29.393999+00:00</t>
   </si>
   <si>
     <t>low</t>
@@ -1330,7 +1330,7 @@
     <t>MWh</t>
   </si>
   <si>
-    <t>2026-10-05T15:22:59.271131+00:00</t>
+    <t>2026-10-12T16:15:23.631333+00:00</t>
   </si>
   <si>
     <t>synthetic scenario: base</t>

--- a/data/outputs/ev_flex_daily_trading_report_sample.xlsx
+++ b/data/outputs/ev_flex_daily_trading_report_sample.xlsx
@@ -49,7 +49,7 @@
     <t>Generated at UTC</t>
   </si>
   <si>
-    <t>2026-10-12T16:15:29.887687+00:00</t>
+    <t>2026-10-19T14:08:39.675584+00:00</t>
   </si>
   <si>
     <t>Data status</t>
@@ -598,151 +598,151 @@
     <t>suggested_action</t>
   </si>
   <si>
-    <t>2026-10-12 16:15:28.217838+00:00</t>
-  </si>
-  <si>
-    <t>2026-10-12 16:15:28.247497+00:00</t>
-  </si>
-  <si>
-    <t>2026-10-12 16:15:28.271987+00:00</t>
-  </si>
-  <si>
-    <t>2026-10-12 16:15:28.304943+00:00</t>
-  </si>
-  <si>
-    <t>2026-10-12 16:15:28.333868+00:00</t>
-  </si>
-  <si>
-    <t>2026-10-12 16:15:28.358228+00:00</t>
-  </si>
-  <si>
-    <t>2026-10-12 16:15:28.375913+00:00</t>
-  </si>
-  <si>
-    <t>2026-10-12 16:15:28.401483+00:00</t>
-  </si>
-  <si>
-    <t>2026-10-12 16:15:28.419661+00:00</t>
-  </si>
-  <si>
-    <t>2026-10-12 16:15:28.439974+00:00</t>
-  </si>
-  <si>
-    <t>2026-10-12 16:15:28.463334+00:00</t>
-  </si>
-  <si>
-    <t>2026-10-12 16:15:28.488509+00:00</t>
-  </si>
-  <si>
-    <t>2026-10-12 16:15:28.507901+00:00</t>
-  </si>
-  <si>
-    <t>2026-10-12 16:15:28.532235+00:00</t>
-  </si>
-  <si>
-    <t>2026-10-12 16:15:28.550205+00:00</t>
-  </si>
-  <si>
-    <t>2026-10-12 16:15:28.568272+00:00</t>
-  </si>
-  <si>
-    <t>2026-10-12 16:15:28.584114+00:00</t>
-  </si>
-  <si>
-    <t>2026-10-12 16:15:28.602455+00:00</t>
-  </si>
-  <si>
-    <t>2026-10-12 16:15:28.626417+00:00</t>
-  </si>
-  <si>
-    <t>2026-10-12 16:15:28.650639+00:00</t>
-  </si>
-  <si>
-    <t>2026-10-12 16:15:28.667863+00:00</t>
-  </si>
-  <si>
-    <t>2026-10-12 16:15:28.681019+00:00</t>
-  </si>
-  <si>
-    <t>2026-10-12 16:15:28.694095+00:00</t>
-  </si>
-  <si>
-    <t>2026-10-12 16:15:28.712002+00:00</t>
-  </si>
-  <si>
-    <t>2026-10-12 16:15:28.762555+00:00</t>
-  </si>
-  <si>
-    <t>2026-10-12 16:15:28.811978+00:00</t>
-  </si>
-  <si>
-    <t>2026-10-12 16:15:28.833698+00:00</t>
-  </si>
-  <si>
-    <t>2026-10-12 16:15:28.864831+00:00</t>
-  </si>
-  <si>
-    <t>2026-10-12 16:15:28.891135+00:00</t>
-  </si>
-  <si>
-    <t>2026-10-12 16:15:28.915330+00:00</t>
-  </si>
-  <si>
-    <t>2026-10-12 16:15:28.933189+00:00</t>
-  </si>
-  <si>
-    <t>2026-10-12 16:15:28.958886+00:00</t>
-  </si>
-  <si>
-    <t>2026-10-12 16:15:28.977045+00:00</t>
-  </si>
-  <si>
-    <t>2026-10-12 16:15:28.997765+00:00</t>
-  </si>
-  <si>
-    <t>2026-10-12 16:15:29.021020+00:00</t>
-  </si>
-  <si>
-    <t>2026-10-12 16:15:29.046190+00:00</t>
-  </si>
-  <si>
-    <t>2026-10-12 16:15:29.065715+00:00</t>
-  </si>
-  <si>
-    <t>2026-10-12 16:15:29.090263+00:00</t>
-  </si>
-  <si>
-    <t>2026-10-12 16:15:29.108151+00:00</t>
-  </si>
-  <si>
-    <t>2026-10-12 16:15:29.126542+00:00</t>
-  </si>
-  <si>
-    <t>2026-10-12 16:15:29.142323+00:00</t>
-  </si>
-  <si>
-    <t>2026-10-12 16:15:29.160486+00:00</t>
-  </si>
-  <si>
-    <t>2026-10-12 16:15:29.184364+00:00</t>
-  </si>
-  <si>
-    <t>2026-10-12 16:15:29.208992+00:00</t>
-  </si>
-  <si>
-    <t>2026-10-12 16:15:29.226104+00:00</t>
-  </si>
-  <si>
-    <t>2026-10-12 16:15:29.239248+00:00</t>
-  </si>
-  <si>
-    <t>2026-10-12 16:15:29.252354+00:00</t>
-  </si>
-  <si>
-    <t>2026-10-12 16:15:29.270367+00:00</t>
-  </si>
-  <si>
-    <t>2026-10-12 16:15:29.393999+00:00</t>
+    <t>2026-10-19 14:08:37.833037+00:00</t>
+  </si>
+  <si>
+    <t>2026-10-19 14:08:37.870100+00:00</t>
+  </si>
+  <si>
+    <t>2026-10-19 14:08:37.897499+00:00</t>
+  </si>
+  <si>
+    <t>2026-10-19 14:08:37.934987+00:00</t>
+  </si>
+  <si>
+    <t>2026-10-19 14:08:37.967079+00:00</t>
+  </si>
+  <si>
+    <t>2026-10-19 14:08:37.994369+00:00</t>
+  </si>
+  <si>
+    <t>2026-10-19 14:08:38.014419+00:00</t>
+  </si>
+  <si>
+    <t>2026-10-19 14:08:38.043245+00:00</t>
+  </si>
+  <si>
+    <t>2026-10-19 14:08:38.063929+00:00</t>
+  </si>
+  <si>
+    <t>2026-10-19 14:08:38.087003+00:00</t>
+  </si>
+  <si>
+    <t>2026-10-19 14:08:38.113126+00:00</t>
+  </si>
+  <si>
+    <t>2026-10-19 14:08:38.141554+00:00</t>
+  </si>
+  <si>
+    <t>2026-10-19 14:08:38.163622+00:00</t>
+  </si>
+  <si>
+    <t>2026-10-19 14:08:38.191078+00:00</t>
+  </si>
+  <si>
+    <t>2026-10-19 14:08:38.211178+00:00</t>
+  </si>
+  <si>
+    <t>2026-10-19 14:08:38.231437+00:00</t>
+  </si>
+  <si>
+    <t>2026-10-19 14:08:38.249102+00:00</t>
+  </si>
+  <si>
+    <t>2026-10-19 14:08:38.269389+00:00</t>
+  </si>
+  <si>
+    <t>2026-10-19 14:08:38.296375+00:00</t>
+  </si>
+  <si>
+    <t>2026-10-19 14:08:38.323428+00:00</t>
+  </si>
+  <si>
+    <t>2026-10-19 14:08:38.342653+00:00</t>
+  </si>
+  <si>
+    <t>2026-10-19 14:08:38.357644+00:00</t>
+  </si>
+  <si>
+    <t>2026-10-19 14:08:38.372402+00:00</t>
+  </si>
+  <si>
+    <t>2026-10-19 14:08:38.392416+00:00</t>
+  </si>
+  <si>
+    <t>2026-10-19 14:08:38.450276+00:00</t>
+  </si>
+  <si>
+    <t>2026-10-19 14:08:38.502971+00:00</t>
+  </si>
+  <si>
+    <t>2026-10-19 14:08:38.527409+00:00</t>
+  </si>
+  <si>
+    <t>2026-10-19 14:08:38.562660+00:00</t>
+  </si>
+  <si>
+    <t>2026-10-19 14:08:38.592858+00:00</t>
+  </si>
+  <si>
+    <t>2026-10-19 14:08:38.620251+00:00</t>
+  </si>
+  <si>
+    <t>2026-10-19 14:08:38.640256+00:00</t>
+  </si>
+  <si>
+    <t>2026-10-19 14:08:38.669290+00:00</t>
+  </si>
+  <si>
+    <t>2026-10-19 14:08:38.689783+00:00</t>
+  </si>
+  <si>
+    <t>2026-10-19 14:08:38.712911+00:00</t>
+  </si>
+  <si>
+    <t>2026-10-19 14:08:38.738949+00:00</t>
+  </si>
+  <si>
+    <t>2026-10-19 14:08:38.767831+00:00</t>
+  </si>
+  <si>
+    <t>2026-10-19 14:08:38.789558+00:00</t>
+  </si>
+  <si>
+    <t>2026-10-19 14:08:38.816911+00:00</t>
+  </si>
+  <si>
+    <t>2026-10-19 14:08:38.837086+00:00</t>
+  </si>
+  <si>
+    <t>2026-10-19 14:08:38.857425+00:00</t>
+  </si>
+  <si>
+    <t>2026-10-19 14:08:38.875182+00:00</t>
+  </si>
+  <si>
+    <t>2026-10-19 14:08:38.895563+00:00</t>
+  </si>
+  <si>
+    <t>2026-10-19 14:08:38.922699+00:00</t>
+  </si>
+  <si>
+    <t>2026-10-19 14:08:38.950220+00:00</t>
+  </si>
+  <si>
+    <t>2026-10-19 14:08:38.969309+00:00</t>
+  </si>
+  <si>
+    <t>2026-10-19 14:08:38.984138+00:00</t>
+  </si>
+  <si>
+    <t>2026-10-19 14:08:38.999030+00:00</t>
+  </si>
+  <si>
+    <t>2026-10-19 14:08:39.018840+00:00</t>
+  </si>
+  <si>
+    <t>2026-10-19 14:08:39.162402+00:00</t>
   </si>
   <si>
     <t>low</t>
@@ -1330,7 +1330,7 @@
     <t>MWh</t>
   </si>
   <si>
-    <t>2026-10-12T16:15:23.631333+00:00</t>
+    <t>2026-10-19T14:08:32.849516+00:00</t>
   </si>
   <si>
     <t>synthetic scenario: base</t>
